--- a/data/trans_dic/P39A5_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,96; 84,41</t>
+          <t>76,22; 84,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,52; 86,98</t>
+          <t>82,54; 86,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,01; 85,15</t>
+          <t>80,99; 85,12</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,64; 92,64</t>
+          <t>86,39; 92,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,37; 88,58</t>
+          <t>74,85; 88,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,37; 89,2</t>
+          <t>82,03; 89,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,87; 93,44</t>
+          <t>88,82; 93,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,88; 90,38</t>
+          <t>85,75; 90,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,12; 91,28</t>
+          <t>88,03; 91,31</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,59; 90,95</t>
+          <t>86,46; 90,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,31; 88,02</t>
+          <t>78,67; 88,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,78; 88,63</t>
+          <t>83,5; 88,52</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>328529; 360360</t>
+          <t>325401; 358956</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504302; 531541</t>
+          <t>504429; 531166</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>840895; 883919</t>
+          <t>840655; 883523</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1863285; 1992393</t>
+          <t>1858081; 1985728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1554082; 1851100</t>
+          <t>1564050; 1850750</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3450485; 3782570</t>
+          <t>3478549; 3781412</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>553122; 581580</t>
+          <t>552832; 580428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>551580; 580453</t>
+          <t>550743; 579932</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1114396; 1154436</t>
+          <t>1113323; 1154732</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2770874; 2910483</t>
+          <t>2766707; 2910257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2617883; 2942587</t>
+          <t>2629875; 2942183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5481857; 5799179</t>
+          <t>5463361; 5791698</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A5_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,22; 84,08</t>
+          <t>76,17; 83,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,54; 86,92</t>
+          <t>82,35; 86,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,99; 85,12</t>
+          <t>80,64; 84,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,33</t>
+          <t>85,27; 88,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,85; 88,57</t>
+          <t>84,46; 87,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,03; 89,18</t>
+          <t>85,29; 87,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,82; 93,25</t>
+          <t>88,34; 92,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,75; 90,29</t>
+          <t>85,5; 89,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,03; 91,31</t>
+          <t>87,64; 90,74</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,46; 90,95</t>
+          <t>85,43; 87,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,67; 88,01</t>
+          <t>84,93; 87,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,5; 88,52</t>
+          <t>85,61; 87,29</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>345287</t>
+          <t>375388</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>518792</t>
+          <t>560694</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>864079</t>
+          <t>936081</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>325401; 358956</t>
+          <t>357062; 392389</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504429; 531166</t>
+          <t>546114; 574006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>840655; 883523</t>
+          <t>912820; 957319</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1908973</t>
+          <t>1791387</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1769264</t>
+          <t>1745463</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3678237</t>
+          <t>3536850</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1858081; 1985728</t>
+          <t>1755999; 1825611</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1564050; 1850750</t>
+          <t>1716159; 1772078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3478549; 3781412</t>
+          <t>3489329; 3578867</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>568644</t>
+          <t>620931</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>566727</t>
+          <t>625495</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1135371</t>
+          <t>1246425</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>552832; 580428</t>
+          <t>603566; 634518</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>550743; 579932</t>
+          <t>609353; 639721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1113323; 1154732</t>
+          <t>1223299; 1266600</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2822904</t>
+          <t>2787706</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2854783</t>
+          <t>2931652</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5677687</t>
+          <t>5719358</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2766707; 2910257</t>
+          <t>2743430; 2823187</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2629875; 2942183</t>
+          <t>2894090; 2965344</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5463361; 5791698</t>
+          <t>5666785; 5777529</t>
         </is>
       </c>
     </row>
